--- a/XmlData/Datas/__beans__.xlsx
+++ b/XmlData/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892A95-BBDD-42B6-A9C8-E869A5FA9CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7250B0E-E5F6-4127-B05C-12AC22B3E030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -80,50 +80,78 @@
   </si>
   <si>
     <t>alias</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>字段别名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>variants</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>字段变体</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TypeOfWord</t>
+  </si>
+  <si>
+    <t>WordChoice</t>
+  </si>
+  <si>
+    <t>(string#sep=,)</t>
+  </si>
+  <si>
+    <t>Enum.CheeseWord</t>
+  </si>
+  <si>
+    <t>WordContent</t>
+  </si>
+  <si>
+    <t>单词</t>
+  </si>
+  <si>
+    <t>词性</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -131,7 +159,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -170,31 +198,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -467,17 +498,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="10" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,7 +548,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -568,14 +601,41 @@
       </c>
       <c r="P3" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="C5" s="4"/>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/XmlData/Datas/__beans__.xlsx
+++ b/XmlData/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7250B0E-E5F6-4127-B05C-12AC22B3E030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864D40C8-9A49-4C20-8428-5D8DEDF52AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23940" yWindow="-360" windowWidth="21600" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>WordChoice</t>
   </si>
   <si>
-    <t>(string#sep=,)</t>
-  </si>
-  <si>
     <t>Enum.CheeseWord</t>
   </si>
   <si>
@@ -114,13 +111,16 @@
   </si>
   <si>
     <t>词性</t>
+  </si>
+  <si>
+    <t>(list#sep=,),string</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +164,11 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -205,7 +210,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -213,12 +218,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -538,15 +546,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -604,30 +612,30 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="4"/>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3"/>
       <c r="J4" t="s">
         <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="4"/>
+    <row r="5" spans="1:16" ht="17.25">
+      <c r="C5" s="3"/>
       <c r="J5" t="s">
         <v>24</v>
       </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>28</v>
+      <c r="L5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/XmlData/Datas/__beans__.xlsx
+++ b/XmlData/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864D40C8-9A49-4C20-8428-5D8DEDF52AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E26AEE-8073-477B-9C0A-2C7BBFD1971D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23940" yWindow="-360" windowWidth="21600" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>WordChoice</t>
   </si>
   <si>
-    <t>Enum.CheeseWord</t>
-  </si>
-  <si>
     <t>WordContent</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>(list#sep=,),string</t>
+  </si>
+  <si>
+    <t>Enum.CheeseWordData</t>
   </si>
 </sst>
 </file>
@@ -223,11 +223,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -546,15 +546,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -613,17 +613,17 @@
     </row>
     <row r="4" spans="1:16">
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3"/>
       <c r="J4" t="s">
         <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="17.25">
@@ -631,11 +631,11 @@
       <c r="J5" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>29</v>
+      <c r="L5" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/XmlData/Datas/__beans__.xlsx
+++ b/XmlData/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E26AEE-8073-477B-9C0A-2C7BBFD1971D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EDE4F2-2780-451A-A669-701396BCD5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,27 @@
   </si>
   <si>
     <t>Enum.CheeseWordData</t>
+  </si>
+  <si>
+    <t>DialogData</t>
+  </si>
+  <si>
+    <t>DialogContent</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>台词</t>
+  </si>
+  <si>
+    <t>对话框</t>
+  </si>
+  <si>
+    <t>Enum.DialogType</t>
+  </si>
+  <si>
+    <t>DialogBoxType</t>
   </si>
 </sst>
 </file>
@@ -170,7 +191,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,8 +210,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -198,6 +225,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -210,7 +246,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -228,6 +264,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -506,14 +554,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="20.5703125" customWidth="1"/>
     <col min="5" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="11" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
   </cols>
@@ -582,47 +631,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16" s="6" customFormat="1">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:16" s="8" customFormat="1">
+      <c r="B4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="J4" t="s">
+      <c r="C4" s="9"/>
+      <c r="J4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="9" t="s">
         <v>27</v>
       </c>
     </row>
@@ -636,6 +685,36 @@
       </c>
       <c r="N5" s="3" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="17.25">
+      <c r="C6" s="3"/>
+      <c r="L6" s="4"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1">
+      <c r="B7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
